--- a/research/traditional_assets/database/data/finland/finland_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_heathcare_information_and_technology.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.5068534876637223</v>
+        <v>-0.5135577372604021</v>
       </c>
       <c r="H2">
-        <v>-0.7761194029850746</v>
+        <v>-0.9340813464235624</v>
       </c>
       <c r="I2">
-        <v>-1.183673469387755</v>
+        <v>-1.12669471715755</v>
       </c>
       <c r="J2">
-        <v>-1.183673469387755</v>
+        <v>-1.12669471715755</v>
       </c>
       <c r="K2">
-        <v>-43.7</v>
+        <v>-48.5</v>
       </c>
       <c r="L2">
-        <v>-1.331099604020713</v>
+        <v>-1.133707339878448</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.362</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0008402971216341689</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.007463917525773195</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,70 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.362</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>150</v>
+        <v>50.01000000000001</v>
       </c>
       <c r="V2">
-        <v>0.2788622420524261</v>
+        <v>0.1160863509749304</v>
       </c>
       <c r="W2">
-        <v>-0.208092485549133</v>
+        <v>-0.2442244224422442</v>
       </c>
       <c r="X2">
-        <v>0.1247909080308362</v>
+        <v>0.1020426194693933</v>
       </c>
       <c r="Y2">
-        <v>-0.3328833935799692</v>
+        <v>-0.3462670419116375</v>
       </c>
       <c r="Z2">
-        <v>1.92100643651258</v>
+        <v>1.396897959183673</v>
+      </c>
+      <c r="AA2">
+        <v>-2.172470978441127</v>
       </c>
       <c r="AB2">
-        <v>0.1228421534091221</v>
+        <v>0.09935165563027647</v>
+      </c>
+      <c r="AC2">
+        <v>-2.271806670353716</v>
       </c>
       <c r="AD2">
-        <v>10.025</v>
+        <v>11.84</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10.025</v>
+        <v>11.84</v>
       </c>
       <c r="AG2">
-        <v>-139.975</v>
+        <v>-38.17</v>
       </c>
       <c r="AH2">
-        <v>0.01829629967605056</v>
+        <v>0.02674859931321164</v>
       </c>
       <c r="AI2">
-        <v>0.0420291374069804</v>
+        <v>0.0572977158343012</v>
       </c>
       <c r="AJ2">
-        <v>-0.3517622667588113</v>
+        <v>-0.09721620864427069</v>
       </c>
       <c r="AK2">
-        <v>-1.581191753741881</v>
+        <v>-0.243695332950265</v>
       </c>
       <c r="AL2">
-        <v>3.096</v>
+        <v>3.22</v>
       </c>
       <c r="AM2">
-        <v>2.887999999999999</v>
+        <v>-1.472999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.3215202052597819</v>
+        <v>-0.3075324675324675</v>
       </c>
       <c r="AO2">
-        <v>-12.55167958656331</v>
+        <v>-14.96894409937888</v>
       </c>
       <c r="AP2">
-        <v>4.489255933290571</v>
+        <v>0.9914285714285714</v>
       </c>
       <c r="AQ2">
-        <v>-13.45567867036011</v>
+        <v>32.72233536999322</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +716,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-4.993527508090615</v>
+        <v>-5.023952095808384</v>
       </c>
       <c r="H3">
-        <v>-6.86084142394822</v>
+        <v>-6.437125748502995</v>
       </c>
       <c r="I3">
-        <v>-6.763754045307444</v>
+        <v>-6.91616766467066</v>
       </c>
       <c r="J3">
-        <v>-6.763754045307444</v>
+        <v>-6.91616766467066</v>
       </c>
       <c r="K3">
-        <v>-21.6</v>
+        <v>-22.2</v>
       </c>
       <c r="L3">
-        <v>-6.990291262135923</v>
+        <v>-6.646706586826348</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,73 +755,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>74.8</v>
+        <v>19.5</v>
       </c>
       <c r="V3">
-        <v>0.2791044776119403</v>
+        <v>0.1419213973799127</v>
       </c>
       <c r="W3">
-        <v>-0.208092485549133</v>
+        <v>-0.2442244224422442</v>
       </c>
       <c r="X3">
-        <v>0.1247909080308362</v>
+        <v>0.1020426194693933</v>
       </c>
       <c r="Y3">
-        <v>-0.3328833935799692</v>
+        <v>-0.3462670419116375</v>
       </c>
       <c r="Z3">
-        <v>0.1808074897600936</v>
+        <v>0.1447767663632422</v>
       </c>
       <c r="AA3">
-        <v>-1.222937390286717</v>
+        <v>-1.001300390117035</v>
       </c>
       <c r="AB3">
-        <v>0.1228421534091221</v>
+        <v>0.09935165563027647</v>
       </c>
       <c r="AC3">
-        <v>-1.345779543695839</v>
+        <v>-1.100652045747311</v>
       </c>
       <c r="AD3">
-        <v>6.97</v>
+        <v>6.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.97</v>
+        <v>6.7</v>
       </c>
       <c r="AG3">
-        <v>-67.83</v>
+        <v>-12.8</v>
       </c>
       <c r="AH3">
-        <v>0.02534821980579699</v>
+        <v>0.04649548924358085</v>
       </c>
       <c r="AI3">
-        <v>0.07121692040461837</v>
+        <v>0.08082026537997587</v>
       </c>
       <c r="AJ3">
-        <v>-0.3388619673277714</v>
+        <v>-0.1027287319422151</v>
       </c>
       <c r="AK3">
-        <v>-2.940182054616384</v>
+        <v>-0.2018927444794953</v>
       </c>
       <c r="AL3">
-        <v>0.254</v>
+        <v>2.83</v>
       </c>
       <c r="AM3">
-        <v>0.168</v>
+        <v>-1.71</v>
       </c>
       <c r="AN3">
-        <v>-0.3538071065989848</v>
+        <v>-0.3145539906103286</v>
       </c>
       <c r="AO3">
-        <v>-82.28346456692913</v>
+        <v>-8.162544169611309</v>
       </c>
       <c r="AP3">
-        <v>3.443147208121828</v>
+        <v>0.6009389671361502</v>
       </c>
       <c r="AQ3">
-        <v>-124.4047619047619</v>
+        <v>13.50877192982456</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nordhealth AS (OB:NORDH)</t>
+          <t>Aiforia Technologies Oyj (HLSE:AIFORIA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,22 +841,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.06760563380281691</v>
+        <v>-3.165178571428572</v>
       </c>
       <c r="H4">
-        <v>0.0369718309859155</v>
+        <v>-4.821428571428571</v>
       </c>
       <c r="I4">
-        <v>-0.3661971830985916</v>
+        <v>-5.848214285714285</v>
       </c>
       <c r="J4">
-        <v>-0.3661971830985916</v>
+        <v>-5.848214285714285</v>
       </c>
       <c r="K4">
-        <v>-12.1</v>
+        <v>-13.6</v>
       </c>
       <c r="L4">
-        <v>-0.426056338028169</v>
+        <v>-6.07142857142857</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -871,64 +880,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>41.3</v>
+        <v>20.8</v>
       </c>
       <c r="V4">
-        <v>0.2285556170448257</v>
+        <v>0.2077922077922078</v>
       </c>
       <c r="W4">
-        <v>-0.09016393442622951</v>
+        <v>-0.3685636856368564</v>
       </c>
       <c r="X4">
-        <v>0.123047573073041</v>
+        <v>0.1021685393328892</v>
       </c>
       <c r="Y4">
-        <v>-0.2132115074992705</v>
+        <v>-0.4707322249697455</v>
+      </c>
+      <c r="Z4">
+        <v>0.3714759535655058</v>
+      </c>
+      <c r="AA4">
+        <v>-2.172470978441127</v>
       </c>
       <c r="AB4">
-        <v>0.1230375999075354</v>
+        <v>0.0993356919125889</v>
+      </c>
+      <c r="AC4">
+        <v>-2.271806670353716</v>
       </c>
       <c r="AD4">
-        <v>0.025</v>
+        <v>5.14</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.025</v>
+        <v>5.14</v>
       </c>
       <c r="AG4">
-        <v>-41.275</v>
+        <v>-15.66</v>
       </c>
       <c r="AH4">
-        <v>0.0001383317194632729</v>
+        <v>0.04884074496389205</v>
       </c>
       <c r="AI4">
-        <v>0.0002482005460412013</v>
+        <v>0.1683038637851997</v>
       </c>
       <c r="AJ4">
-        <v>-0.2960372960372961</v>
+        <v>-0.1854571293225959</v>
       </c>
       <c r="AK4">
-        <v>-0.6945729911653343</v>
+        <v>-1.607802874743327</v>
       </c>
       <c r="AL4">
-        <v>0.022</v>
+        <v>0.385</v>
       </c>
       <c r="AM4">
-        <v>0.022</v>
+        <v>0.232</v>
       </c>
       <c r="AN4">
-        <v>-0.007485029940119761</v>
+        <v>-0.3697841726618705</v>
       </c>
       <c r="AO4">
-        <v>-472.7272727272727</v>
+        <v>-34.02597402597402</v>
       </c>
       <c r="AP4">
-        <v>12.35778443113773</v>
+        <v>1.126618705035971</v>
       </c>
       <c r="AQ4">
-        <v>-472.7272727272727</v>
+        <v>-56.4655172413793</v>
       </c>
     </row>
     <row r="5">
@@ -939,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aiforia Technologies Oyj (HLSE:AIFORIA)</t>
+          <t>Nordhealth AS (OB:NORDH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -948,31 +966,31 @@
         </is>
       </c>
       <c r="G5">
-        <v>-2.335820895522388</v>
+        <v>0.0510752688172043</v>
       </c>
       <c r="H5">
-        <v>-3.977611940298507</v>
+        <v>-0.2059139784946236</v>
       </c>
       <c r="I5">
-        <v>-5.641791044776118</v>
+        <v>-0.3225806451612903</v>
       </c>
       <c r="J5">
-        <v>-5.641791044776118</v>
+        <v>-0.3225806451612903</v>
       </c>
       <c r="K5">
-        <v>-10</v>
+        <v>-12.7</v>
       </c>
       <c r="L5">
-        <v>-7.462686567164178</v>
+        <v>-0.3413978494623656</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.362</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.001872736678737713</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0.02850393700787402</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -984,61 +1002,79 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.362</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>33.9</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="V5">
-        <v>0.3800448430493273</v>
+        <v>0.05023279875840662</v>
+      </c>
+      <c r="W5">
+        <v>-0.1261171797418073</v>
       </c>
       <c r="X5">
-        <v>0.1253274145128905</v>
+        <v>0.09966814174204705</v>
+      </c>
+      <c r="Y5">
+        <v>-0.2257853214838544</v>
+      </c>
+      <c r="Z5">
+        <v>24.39344262295062</v>
+      </c>
+      <c r="AA5">
+        <v>-7.868852459016328</v>
       </c>
       <c r="AB5">
-        <v>0.1225817261220634</v>
+        <v>0.09966814174204705</v>
+      </c>
+      <c r="AC5">
+        <v>-7.968520600758374</v>
       </c>
       <c r="AD5">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-30.87</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.03285265098124254</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.07588279489105935</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.5292302417280986</v>
+        <v>-0.05288959093632551</v>
       </c>
       <c r="AK5">
-        <v>-5.119402985074625</v>
+        <v>-0.1163013534555036</v>
       </c>
       <c r="AL5">
-        <v>2.82</v>
+        <v>0.005</v>
       </c>
       <c r="AM5">
-        <v>2.698</v>
+        <v>0.005</v>
       </c>
       <c r="AN5">
-        <v>-0.3722358722358722</v>
+        <v>-0</v>
       </c>
       <c r="AO5">
-        <v>-2.680851063829787</v>
+        <v>-2400</v>
       </c>
       <c r="AP5">
-        <v>3.792383292383292</v>
+        <v>2.942424242424243</v>
       </c>
       <c r="AQ5">
-        <v>-2.802075611564121</v>
+        <v>-2400</v>
       </c>
     </row>
   </sheetData>
